--- a/source-data/Human/participant_demographics.xlsx
+++ b/source-data/Human/participant_demographics.xlsx
@@ -5,7 +5,7 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\PythonProject\classifier-variability\source-data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\PythonProject\classifier-variability\source-data\Human\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -34,14 +34,11 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="356" uniqueCount="206">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="305" uniqueCount="155">
   <si>
     <t>学号</t>
   </si>
   <si>
-    <t>姓名</t>
-  </si>
-  <si>
     <t>性别</t>
   </si>
   <si>
@@ -60,9 +57,6 @@
     <t>2024120349</t>
   </si>
   <si>
-    <t>万灵思</t>
-  </si>
-  <si>
     <t>女</t>
   </si>
   <si>
@@ -81,9 +75,6 @@
     <t>2024210318</t>
   </si>
   <si>
-    <t>罗洁梅</t>
-  </si>
-  <si>
     <t>20</t>
   </si>
   <si>
@@ -96,9 +87,6 @@
     <t>2024214268</t>
   </si>
   <si>
-    <t>曾倩</t>
-  </si>
-  <si>
     <t>软件工程</t>
   </si>
   <si>
@@ -108,9 +96,6 @@
     <t>2024214670</t>
   </si>
   <si>
-    <t>胡焙鑫</t>
-  </si>
-  <si>
     <t>19</t>
   </si>
   <si>
@@ -123,9 +108,6 @@
     <t>2024214738</t>
   </si>
   <si>
-    <t>张晓雅</t>
-  </si>
-  <si>
     <t>大数据</t>
   </si>
   <si>
@@ -135,9 +117,6 @@
     <t>2024215567</t>
   </si>
   <si>
-    <t>刘秋芳</t>
-  </si>
-  <si>
     <t>地理科学</t>
   </si>
   <si>
@@ -147,9 +126,6 @@
     <t>2025114888</t>
   </si>
   <si>
-    <t>喻安楠</t>
-  </si>
-  <si>
     <t>22</t>
   </si>
   <si>
@@ -162,9 +138,6 @@
     <t>2025123891</t>
   </si>
   <si>
-    <t>康文军</t>
-  </si>
-  <si>
     <t>男</t>
   </si>
   <si>
@@ -177,9 +150,6 @@
     <t>2025124932</t>
   </si>
   <si>
-    <t>刘孟孟</t>
-  </si>
-  <si>
     <t>23</t>
   </si>
   <si>
@@ -192,9 +162,6 @@
     <t>2025210331</t>
   </si>
   <si>
-    <t>赵雅淇</t>
-  </si>
-  <si>
     <t>18</t>
   </si>
   <si>
@@ -207,9 +174,6 @@
     <t>2023214841</t>
   </si>
   <si>
-    <t>段雪舒</t>
-  </si>
-  <si>
     <t>21</t>
   </si>
   <si>
@@ -222,9 +186,6 @@
     <t>2024214430</t>
   </si>
   <si>
-    <t>崔文馨</t>
-  </si>
-  <si>
     <t>教育技术学师范</t>
   </si>
   <si>
@@ -234,9 +195,6 @@
     <t>2025113823</t>
   </si>
   <si>
-    <t>刘文依</t>
-  </si>
-  <si>
     <t>计算机科学与技术</t>
   </si>
   <si>
@@ -246,9 +204,6 @@
     <t>2025114457</t>
   </si>
   <si>
-    <t>王亚鹏</t>
-  </si>
-  <si>
     <t>政治学</t>
   </si>
   <si>
@@ -258,9 +213,6 @@
     <t>2025120825</t>
   </si>
   <si>
-    <t>周玉芬</t>
-  </si>
-  <si>
     <t>特殊教育</t>
   </si>
   <si>
@@ -270,9 +222,6 @@
     <t>2025123865</t>
   </si>
   <si>
-    <t>王旭</t>
-  </si>
-  <si>
     <t>计算机技术</t>
   </si>
   <si>
@@ -282,9 +231,6 @@
     <t>2025123878</t>
   </si>
   <si>
-    <t>李阳春</t>
-  </si>
-  <si>
     <t>26</t>
   </si>
   <si>
@@ -294,9 +240,6 @@
     <t>2025210984</t>
   </si>
   <si>
-    <t>王宇轩</t>
-  </si>
-  <si>
     <t>化学</t>
   </si>
   <si>
@@ -306,9 +249,6 @@
     <t>2025212461</t>
   </si>
   <si>
-    <t>朱一凡</t>
-  </si>
-  <si>
     <t>历史学</t>
   </si>
   <si>
@@ -318,9 +258,6 @@
     <t>2025215102</t>
   </si>
   <si>
-    <t>陈瑞琪</t>
-  </si>
-  <si>
     <t>外院</t>
   </si>
   <si>
@@ -330,9 +267,6 @@
     <t>2022215358</t>
   </si>
   <si>
-    <t>王晗</t>
-  </si>
-  <si>
     <t>生命技术专业</t>
   </si>
   <si>
@@ -345,9 +279,6 @@
     <t>2023211058</t>
   </si>
   <si>
-    <t>张诗媛</t>
-  </si>
-  <si>
     <t>汉语言</t>
   </si>
   <si>
@@ -357,9 +288,6 @@
     <t>2023214857</t>
   </si>
   <si>
-    <t>郭君茹</t>
-  </si>
-  <si>
     <t>科学教育</t>
   </si>
   <si>
@@ -369,9 +297,6 @@
     <t>2024112616</t>
   </si>
   <si>
-    <t>廖琴</t>
-  </si>
-  <si>
     <t>地理学</t>
   </si>
   <si>
@@ -381,9 +306,6 @@
     <t>2024212820</t>
   </si>
   <si>
-    <t>余启菲</t>
-  </si>
-  <si>
     <t>物理学</t>
   </si>
   <si>
@@ -393,18 +315,12 @@
     <t>2024214425</t>
   </si>
   <si>
-    <t>成雨芮</t>
-  </si>
-  <si>
     <t>184.44</t>
   </si>
   <si>
     <t>2024215043</t>
   </si>
   <si>
-    <t>张睿琪</t>
-  </si>
-  <si>
     <t>电子商务</t>
   </si>
   <si>
@@ -414,9 +330,6 @@
     <t>2024215153</t>
   </si>
   <si>
-    <t>何润鑫</t>
-  </si>
-  <si>
     <t>财务会计教育</t>
   </si>
   <si>
@@ -426,27 +339,18 @@
     <t>2025113831</t>
   </si>
   <si>
-    <t>陈柳含</t>
-  </si>
-  <si>
     <t>210.35</t>
   </si>
   <si>
     <t>2025123907</t>
   </si>
   <si>
-    <t>高枫</t>
-  </si>
-  <si>
     <t>209.26</t>
   </si>
   <si>
     <t>2023211059</t>
   </si>
   <si>
-    <t>吕琪琪</t>
-  </si>
-  <si>
     <t>4</t>
   </si>
   <si>
@@ -456,9 +360,6 @@
     <t>2024212515</t>
   </si>
   <si>
-    <t>袁阳蕾</t>
-  </si>
-  <si>
     <t>物理</t>
   </si>
   <si>
@@ -468,9 +369,6 @@
     <t>2024212695</t>
   </si>
   <si>
-    <t>周鑫</t>
-  </si>
-  <si>
     <t>物理学师范</t>
   </si>
   <si>
@@ -480,18 +378,12 @@
     <t>2024213711</t>
   </si>
   <si>
-    <t>陈晓美</t>
-  </si>
-  <si>
     <t>219.18</t>
   </si>
   <si>
     <t>2024215136</t>
   </si>
   <si>
-    <t>江子颖</t>
-  </si>
-  <si>
     <t>经济学</t>
   </si>
   <si>
@@ -501,18 +393,12 @@
     <t>2025113836</t>
   </si>
   <si>
-    <t>陈垂灿</t>
-  </si>
-  <si>
     <t>204.28</t>
   </si>
   <si>
     <t>2025123234</t>
   </si>
   <si>
-    <t>王雨桐</t>
-  </si>
-  <si>
     <t>体育教学</t>
   </si>
   <si>
@@ -522,27 +408,18 @@
     <t>2025123843</t>
   </si>
   <si>
-    <t>杨佳杰</t>
-  </si>
-  <si>
     <t>194.88</t>
   </si>
   <si>
     <t>2025123859</t>
   </si>
   <si>
-    <t>宋宇豪</t>
-  </si>
-  <si>
     <t>174.34</t>
   </si>
   <si>
     <t>2025217822</t>
   </si>
   <si>
-    <t>陆筱欢</t>
-  </si>
-  <si>
     <t>音乐学</t>
   </si>
   <si>
@@ -552,9 +429,6 @@
     <t>2022214287</t>
   </si>
   <si>
-    <t>俞兴</t>
-  </si>
-  <si>
     <t>5</t>
   </si>
   <si>
@@ -564,27 +438,18 @@
     <t>2023214849</t>
   </si>
   <si>
-    <t>赵婉竹</t>
-  </si>
-  <si>
     <t>210.25</t>
   </si>
   <si>
     <t>2024123581</t>
   </si>
   <si>
-    <t>张雅芸</t>
-  </si>
-  <si>
     <t>189.71</t>
   </si>
   <si>
     <t>2024211668</t>
   </si>
   <si>
-    <t>叶福劲</t>
-  </si>
-  <si>
     <t>西英复语</t>
   </si>
   <si>
@@ -594,27 +459,18 @@
     <t>2024213709</t>
   </si>
   <si>
-    <t>张慧茹</t>
-  </si>
-  <si>
     <t>179.3</t>
   </si>
   <si>
     <t>2025120351</t>
   </si>
   <si>
-    <t>曹吉安</t>
-  </si>
-  <si>
     <t>183.9</t>
   </si>
   <si>
     <t>2025120978</t>
   </si>
   <si>
-    <t>林丽丹</t>
-  </si>
-  <si>
     <t>心理健康教育</t>
   </si>
   <si>
@@ -624,9 +480,6 @@
     <t>2025163319</t>
   </si>
   <si>
-    <t>范思源</t>
-  </si>
-  <si>
     <t>社会体育指导</t>
   </si>
   <si>
@@ -636,16 +489,10 @@
     <t>2025210914</t>
   </si>
   <si>
-    <t>杨吕</t>
-  </si>
-  <si>
     <t>205.66</t>
   </si>
   <si>
     <t>2025212002</t>
-  </si>
-  <si>
-    <t>刘城伟</t>
   </si>
   <si>
     <t>数学与经济交叉专业</t>
@@ -1593,13 +1440,13 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:G51"/>
-  <sheetFormatPr defaultColWidth="9.23148148148148" defaultRowHeight="14.4" outlineLevelCol="6"/>
+  <dimension ref="A1:F51"/>
+  <sheetFormatPr defaultColWidth="9.23148148148148" defaultRowHeight="14.4" outlineLevelCol="5"/>
   <cols>
     <col min="1" max="16384" width="9.23148148148148" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1" ht="15.6" spans="1:7">
+    <row r="1" s="1" customFormat="1" ht="15.6" spans="1:6">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -1618,1156 +1465,1003 @@
       <c r="F1" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="2" t="s">
+    </row>
+    <row r="2" s="1" customFormat="1" ht="15.6" spans="1:6">
+      <c r="A2" s="2" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="2" s="1" customFormat="1" ht="15.6" spans="1:7">
-      <c r="A2" s="2" t="s">
-        <v>7</v>
-      </c>
       <c r="B2" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="C2" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="C2" s="2" t="s">
+      <c r="D2" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="D2" s="2" t="s">
+      <c r="E2" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="E2" s="2" t="s">
+      <c r="F2" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="F2" s="2" t="s">
+    </row>
+    <row r="3" s="1" customFormat="1" ht="15.6" spans="1:6">
+      <c r="A3" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="G2" s="2" t="s">
+      <c r="B3" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="C3" s="2" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="3" s="1" customFormat="1" ht="15.6" spans="1:7">
-      <c r="A3" s="2" t="s">
+      <c r="D3" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="B3" s="2" t="s">
+      <c r="E3" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="F3" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="C3" s="2" t="s">
+    </row>
+    <row r="4" s="1" customFormat="1" ht="15.6" spans="1:6">
+      <c r="A4" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="E4" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="F4" s="2" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="5" s="1" customFormat="1" ht="15.6" spans="1:6">
+      <c r="A5" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="E5" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="F5" s="2" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="6" s="1" customFormat="1" ht="15.6" spans="1:6">
+      <c r="A6" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="E6" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="F6" s="2" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="7" s="1" customFormat="1" ht="15.6" spans="1:6">
+      <c r="A7" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="E7" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="F7" s="2" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="8" s="1" customFormat="1" ht="15.6" spans="1:6">
+      <c r="A8" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="E8" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="F8" s="2" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="9" s="1" customFormat="1" ht="15.6" spans="1:6">
+      <c r="A9" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="E9" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="F9" s="2" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="10" s="1" customFormat="1" ht="15.6" spans="1:6">
+      <c r="A10" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="D10" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="E10" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="F10" s="2" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="11" s="1" customFormat="1" ht="15.6" spans="1:6">
+      <c r="A11" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="C11" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="D11" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="E11" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="F11" s="2" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="12" s="1" customFormat="1" ht="15.6" spans="1:6">
+      <c r="A12" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="C12" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="D12" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="E12" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="F12" s="2" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="13" s="1" customFormat="1" ht="15.6" spans="1:6">
+      <c r="A13" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="B13" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="C13" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="D13" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="E13" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="F13" s="2" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="14" s="1" customFormat="1" ht="15.6" spans="1:6">
+      <c r="A14" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="B14" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="C14" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="D14" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="E14" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="F14" s="2" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="15" s="1" customFormat="1" ht="15.6" spans="1:6">
+      <c r="A15" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="B15" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="C15" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D15" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="E15" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="F15" s="2" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="16" s="1" customFormat="1" ht="15.6" spans="1:6">
+      <c r="A16" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="B16" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="C16" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="D16" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="E16" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="F16" s="2" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="17" s="1" customFormat="1" ht="15.6" spans="1:6">
+      <c r="A17" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="B17" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="C17" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D17" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="E17" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="F17" s="2" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="18" s="1" customFormat="1" ht="15.6" spans="1:6">
+      <c r="A18" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="B18" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="C18" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="D18" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="E18" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="F18" s="2" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="19" s="1" customFormat="1" ht="15.6" spans="1:6">
+      <c r="A19" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="B19" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="C19" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="D19" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="E19" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="F19" s="2" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="20" s="1" customFormat="1" ht="15.6" spans="1:6">
+      <c r="A20" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="B20" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="C20" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="D20" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="E20" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="F20" s="2" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="21" s="1" customFormat="1" ht="15.6" spans="1:6">
+      <c r="A21" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="B21" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="C21" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="D21" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="E21" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="F21" s="2" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="22" s="1" customFormat="1" ht="15.6" spans="1:6">
+      <c r="A22" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="B22" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="C22" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="D22" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="E22" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="F22" s="2" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="23" s="1" customFormat="1" ht="15.6" spans="1:6">
+      <c r="A23" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="B23" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="C23" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="D23" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="E23" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="F23" s="2" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="24" s="1" customFormat="1" ht="15.6" spans="1:6">
+      <c r="A24" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="B24" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="C24" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="D24" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="E24" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="F24" s="2" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="25" s="1" customFormat="1" ht="15.6" spans="1:6">
+      <c r="A25" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="B25" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="C25" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D25" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="E25" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="F25" s="2" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="26" s="1" customFormat="1" ht="15.6" spans="1:6">
+      <c r="A26" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="B26" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="C26" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="D26" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="E26" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="F26" s="2" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="27" s="1" customFormat="1" ht="15.6" spans="1:6">
+      <c r="A27" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="B27" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="C27" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="D27" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="E27" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="F27" s="2" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="28" s="1" customFormat="1" ht="15.6" spans="1:6">
+      <c r="A28" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="B28" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="C28" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="D28" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="E28" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="F28" s="2" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="29" s="1" customFormat="1" ht="15.6" spans="1:6">
+      <c r="A29" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="B29" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="C29" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="D29" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="E29" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="F29" s="2" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="30" s="1" customFormat="1" ht="15.6" spans="1:6">
+      <c r="A30" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="B30" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="C30" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="D30" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="E30" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="F30" s="2" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="31" s="1" customFormat="1" ht="15.6" spans="1:6">
+      <c r="A31" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="B31" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="C31" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="D31" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="E31" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="F31" s="2" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="32" s="1" customFormat="1" ht="15.6" spans="1:6">
+      <c r="A32" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="B32" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="C32" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="D32" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="E32" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="F32" s="2" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="33" s="1" customFormat="1" ht="15.6" spans="1:6">
+      <c r="A33" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="B33" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="C33" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="D33" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="E33" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="F33" s="2" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="34" s="1" customFormat="1" ht="15.6" spans="1:6">
+      <c r="A34" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="B34" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="C34" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="D34" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="E34" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="F34" s="2" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="35" s="1" customFormat="1" ht="15.6" spans="1:6">
+      <c r="A35" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="B35" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="C35" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="D35" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="E35" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="F35" s="2" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="36" s="1" customFormat="1" ht="15.6" spans="1:6">
+      <c r="A36" s="2" t="s">
+        <v>115</v>
+      </c>
+      <c r="B36" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="C36" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="D36" s="2" t="s">
+        <v>116</v>
+      </c>
+      <c r="E36" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="F36" s="2" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="37" s="1" customFormat="1" ht="15.6" spans="1:6">
+      <c r="A37" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="B37" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="C37" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="D37" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="E37" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="F37" s="2" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="38" s="1" customFormat="1" ht="15.6" spans="1:6">
+      <c r="A38" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="B38" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="C38" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="D38" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="E38" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="F38" s="2" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="39" s="1" customFormat="1" ht="15.6" spans="1:6">
+      <c r="A39" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="B39" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="C39" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="D39" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="E39" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="F39" s="2" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="40" s="1" customFormat="1" ht="15.6" spans="1:6">
+      <c r="A40" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="B40" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="C40" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D40" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="E40" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="F40" s="2" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="41" s="1" customFormat="1" ht="15.6" spans="1:6">
+      <c r="A41" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="B41" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="C41" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="D41" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="E41" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="F41" s="2" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="42" s="1" customFormat="1" ht="15.6" spans="1:6">
+      <c r="A42" s="2" t="s">
+        <v>130</v>
+      </c>
+      <c r="B42" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="C42" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="D42" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="E42" s="2" t="s">
+        <v>131</v>
+      </c>
+      <c r="F42" s="2" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="43" s="1" customFormat="1" ht="15.6" spans="1:6">
+      <c r="A43" s="2" t="s">
+        <v>133</v>
+      </c>
+      <c r="B43" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="C43" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="D43" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="E43" s="2" t="s">
+        <v>131</v>
+      </c>
+      <c r="F43" s="2" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="44" s="1" customFormat="1" ht="15.6" spans="1:6">
+      <c r="A44" s="2" t="s">
+        <v>135</v>
+      </c>
+      <c r="B44" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="C44" s="2"/>
+      <c r="D44" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="E44" s="2" t="s">
+        <v>131</v>
+      </c>
+      <c r="F44" s="2" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="45" s="1" customFormat="1" ht="15.6" spans="1:6">
+      <c r="A45" s="2" t="s">
+        <v>137</v>
+      </c>
+      <c r="B45" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="C45" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="D45" s="2" t="s">
+        <v>138</v>
+      </c>
+      <c r="E45" s="2" t="s">
+        <v>131</v>
+      </c>
+      <c r="F45" s="2" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="46" s="1" customFormat="1" ht="15.6" spans="1:6">
+      <c r="A46" s="2" t="s">
+        <v>140</v>
+      </c>
+      <c r="B46" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="C46" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="D46" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="E46" s="2" t="s">
+        <v>131</v>
+      </c>
+      <c r="F46" s="2" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="47" s="1" customFormat="1" ht="15.6" spans="1:6">
+      <c r="A47" s="2" t="s">
+        <v>142</v>
+      </c>
+      <c r="B47" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="C47" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="D47" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="D3" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="E3" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="F3" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="G3" s="2" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="4" s="1" customFormat="1" ht="15.6" spans="1:7">
-      <c r="A4" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="B4" s="2" t="s">
+      <c r="E47" s="2" t="s">
+        <v>131</v>
+      </c>
+      <c r="F47" s="2" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="48" s="1" customFormat="1" ht="15.6" spans="1:6">
+      <c r="A48" s="2" t="s">
+        <v>144</v>
+      </c>
+      <c r="B48" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="C48" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="D48" s="2" t="s">
+        <v>145</v>
+      </c>
+      <c r="E48" s="2" t="s">
+        <v>131</v>
+      </c>
+      <c r="F48" s="2" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="49" s="1" customFormat="1" ht="15.6" spans="1:6">
+      <c r="A49" s="2" t="s">
+        <v>147</v>
+      </c>
+      <c r="B49" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="C49" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="D49" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="E49" s="2" t="s">
+        <v>131</v>
+      </c>
+      <c r="F49" s="2" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="50" s="1" customFormat="1" ht="15.6" spans="1:6">
+      <c r="A50" s="2" t="s">
+        <v>150</v>
+      </c>
+      <c r="B50" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="C50" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="D50" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="E50" s="2" t="s">
+        <v>131</v>
+      </c>
+      <c r="F50" s="2" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="51" s="1" customFormat="1" ht="15.6" spans="1:6">
+      <c r="A51" s="2" t="s">
+        <v>152</v>
+      </c>
+      <c r="B51" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="C51" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="C4" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D4" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="E4" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="F4" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="G4" s="2" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="5" s="1" customFormat="1" ht="15.6" spans="1:7">
-      <c r="A5" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="B5" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="C5" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D5" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="E5" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="F5" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="G5" s="2" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="6" s="1" customFormat="1" ht="15.6" spans="1:7">
-      <c r="A6" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="B6" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="C6" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D6" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="E6" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="F6" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="G6" s="2" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="7" s="1" customFormat="1" ht="15.6" spans="1:7">
-      <c r="A7" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="B7" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="C7" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D7" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="E7" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="F7" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="G7" s="2" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="8" s="1" customFormat="1" ht="15.6" spans="1:7">
-      <c r="A8" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="B8" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="C8" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D8" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="E8" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="F8" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="G8" s="2" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="9" s="1" customFormat="1" ht="15.6" spans="1:7">
-      <c r="A9" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="B9" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="C9" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="D9" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="E9" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="F9" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="G9" s="2" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="10" s="1" customFormat="1" ht="15.6" spans="1:7">
-      <c r="A10" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="B10" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="C10" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D10" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="E10" s="2" t="s">
-        <v>49</v>
-      </c>
-      <c r="F10" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="G10" s="2" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="11" s="1" customFormat="1" ht="15.6" spans="1:7">
-      <c r="A11" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="B11" s="2" t="s">
-        <v>52</v>
-      </c>
-      <c r="C11" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D11" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="E11" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="F11" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="G11" s="2" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="12" s="1" customFormat="1" ht="15.6" spans="1:7">
-      <c r="A12" s="2" t="s">
-        <v>56</v>
-      </c>
-      <c r="B12" s="2" t="s">
-        <v>57</v>
-      </c>
-      <c r="C12" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D12" s="2" t="s">
-        <v>58</v>
-      </c>
-      <c r="E12" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="F12" s="2" t="s">
-        <v>59</v>
-      </c>
-      <c r="G12" s="2" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="13" s="1" customFormat="1" ht="15.6" spans="1:7">
-      <c r="A13" s="2" t="s">
-        <v>61</v>
-      </c>
-      <c r="B13" s="2" t="s">
-        <v>62</v>
-      </c>
-      <c r="C13" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D13" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="E13" s="2" t="s">
-        <v>63</v>
-      </c>
-      <c r="F13" s="2" t="s">
-        <v>59</v>
-      </c>
-      <c r="G13" s="2" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="14" s="1" customFormat="1" ht="15.6" spans="1:7">
-      <c r="A14" s="2" t="s">
-        <v>65</v>
-      </c>
-      <c r="B14" s="2" t="s">
-        <v>66</v>
-      </c>
-      <c r="C14" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D14" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="E14" s="2" t="s">
-        <v>67</v>
-      </c>
-      <c r="F14" s="2" t="s">
-        <v>59</v>
-      </c>
-      <c r="G14" s="2" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="15" s="1" customFormat="1" ht="15.6" spans="1:7">
-      <c r="A15" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="B15" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="C15" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="D15" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="E15" s="2" t="s">
-        <v>71</v>
-      </c>
-      <c r="F15" s="2" t="s">
-        <v>59</v>
-      </c>
-      <c r="G15" s="2" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="16" s="1" customFormat="1" ht="15.6" spans="1:7">
-      <c r="A16" s="2" t="s">
-        <v>73</v>
-      </c>
-      <c r="B16" s="2" t="s">
-        <v>74</v>
-      </c>
-      <c r="C16" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D16" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="E16" s="2" t="s">
-        <v>75</v>
-      </c>
-      <c r="F16" s="2" t="s">
-        <v>59</v>
-      </c>
-      <c r="G16" s="2" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="17" s="1" customFormat="1" ht="15.6" spans="1:7">
-      <c r="A17" s="2" t="s">
-        <v>77</v>
-      </c>
-      <c r="B17" s="2" t="s">
-        <v>78</v>
-      </c>
-      <c r="C17" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="D17" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="E17" s="2" t="s">
-        <v>79</v>
-      </c>
-      <c r="F17" s="2" t="s">
-        <v>59</v>
-      </c>
-      <c r="G17" s="2" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="18" s="1" customFormat="1" ht="15.6" spans="1:7">
-      <c r="A18" s="2" t="s">
-        <v>81</v>
-      </c>
-      <c r="B18" s="2" t="s">
-        <v>82</v>
-      </c>
-      <c r="C18" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="D18" s="2" t="s">
-        <v>83</v>
-      </c>
-      <c r="E18" s="2" t="s">
-        <v>79</v>
-      </c>
-      <c r="F18" s="2" t="s">
-        <v>59</v>
-      </c>
-      <c r="G18" s="2" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="19" s="1" customFormat="1" ht="15.6" spans="1:7">
-      <c r="A19" s="2" t="s">
-        <v>85</v>
-      </c>
-      <c r="B19" s="2" t="s">
-        <v>86</v>
-      </c>
-      <c r="C19" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="D19" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="E19" s="2" t="s">
-        <v>87</v>
-      </c>
-      <c r="F19" s="2" t="s">
-        <v>59</v>
-      </c>
-      <c r="G19" s="2" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="20" s="1" customFormat="1" ht="15.6" spans="1:7">
-      <c r="A20" s="2" t="s">
-        <v>89</v>
-      </c>
-      <c r="B20" s="2" t="s">
-        <v>90</v>
-      </c>
-      <c r="C20" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D20" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="E20" s="2" t="s">
-        <v>91</v>
-      </c>
-      <c r="F20" s="2" t="s">
-        <v>59</v>
-      </c>
-      <c r="G20" s="2" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="21" s="1" customFormat="1" ht="15.6" spans="1:7">
-      <c r="A21" s="2" t="s">
-        <v>93</v>
-      </c>
-      <c r="B21" s="2" t="s">
-        <v>94</v>
-      </c>
-      <c r="C21" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D21" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="E21" s="2" t="s">
-        <v>95</v>
-      </c>
-      <c r="F21" s="2" t="s">
-        <v>59</v>
-      </c>
-      <c r="G21" s="2" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="22" s="1" customFormat="1" ht="15.6" spans="1:7">
-      <c r="A22" s="2" t="s">
-        <v>97</v>
-      </c>
-      <c r="B22" s="2" t="s">
-        <v>98</v>
-      </c>
-      <c r="C22" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D22" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="E22" s="2" t="s">
-        <v>99</v>
-      </c>
-      <c r="F22" s="2" t="s">
-        <v>100</v>
-      </c>
-      <c r="G22" s="2" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="23" s="1" customFormat="1" ht="15.6" spans="1:7">
-      <c r="A23" s="2" t="s">
-        <v>102</v>
-      </c>
-      <c r="B23" s="2" t="s">
-        <v>103</v>
-      </c>
-      <c r="C23" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D23" s="2" t="s">
-        <v>58</v>
-      </c>
-      <c r="E23" s="2" t="s">
-        <v>104</v>
-      </c>
-      <c r="F23" s="2" t="s">
-        <v>100</v>
-      </c>
-      <c r="G23" s="2" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="24" s="1" customFormat="1" ht="15.6" spans="1:7">
-      <c r="A24" s="2" t="s">
-        <v>106</v>
-      </c>
-      <c r="B24" s="2" t="s">
-        <v>107</v>
-      </c>
-      <c r="C24" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D24" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="E24" s="2" t="s">
-        <v>108</v>
-      </c>
-      <c r="F24" s="2" t="s">
-        <v>100</v>
-      </c>
-      <c r="G24" s="2" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="25" s="1" customFormat="1" ht="15.6" spans="1:7">
-      <c r="A25" s="2" t="s">
-        <v>110</v>
-      </c>
-      <c r="B25" s="2" t="s">
-        <v>111</v>
-      </c>
-      <c r="C25" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D25" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="E25" s="2" t="s">
-        <v>112</v>
-      </c>
-      <c r="F25" s="2" t="s">
-        <v>100</v>
-      </c>
-      <c r="G25" s="2" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="26" s="1" customFormat="1" ht="15.6" spans="1:7">
-      <c r="A26" s="2" t="s">
-        <v>114</v>
-      </c>
-      <c r="B26" s="2" t="s">
-        <v>115</v>
-      </c>
-      <c r="C26" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D26" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="E26" s="2" t="s">
-        <v>116</v>
-      </c>
-      <c r="F26" s="2" t="s">
-        <v>100</v>
-      </c>
-      <c r="G26" s="2" t="s">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="27" s="1" customFormat="1" ht="15.6" spans="1:7">
-      <c r="A27" s="2" t="s">
-        <v>118</v>
-      </c>
-      <c r="B27" s="2" t="s">
-        <v>119</v>
-      </c>
-      <c r="C27" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D27" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="E27" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="F27" s="2" t="s">
-        <v>100</v>
-      </c>
-      <c r="G27" s="2" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="28" s="1" customFormat="1" ht="15.6" spans="1:7">
-      <c r="A28" s="2" t="s">
-        <v>121</v>
-      </c>
-      <c r="B28" s="2" t="s">
-        <v>122</v>
-      </c>
-      <c r="C28" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D28" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="E28" s="2" t="s">
-        <v>123</v>
-      </c>
-      <c r="F28" s="2" t="s">
-        <v>100</v>
-      </c>
-      <c r="G28" s="2" t="s">
-        <v>124</v>
-      </c>
-    </row>
-    <row r="29" s="1" customFormat="1" ht="15.6" spans="1:7">
-      <c r="A29" s="2" t="s">
-        <v>125</v>
-      </c>
-      <c r="B29" s="2" t="s">
-        <v>126</v>
-      </c>
-      <c r="C29" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D29" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="E29" s="2" t="s">
-        <v>127</v>
-      </c>
-      <c r="F29" s="2" t="s">
-        <v>100</v>
-      </c>
-      <c r="G29" s="2" t="s">
-        <v>128</v>
-      </c>
-    </row>
-    <row r="30" s="1" customFormat="1" ht="15.6" spans="1:7">
-      <c r="A30" s="2" t="s">
-        <v>129</v>
-      </c>
-      <c r="B30" s="2" t="s">
-        <v>130</v>
-      </c>
-      <c r="C30" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D30" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="E30" s="2" t="s">
-        <v>67</v>
-      </c>
-      <c r="F30" s="2" t="s">
-        <v>100</v>
-      </c>
-      <c r="G30" s="2" t="s">
+      <c r="D51" s="2" t="s">
+        <v>153</v>
+      </c>
+      <c r="E51" s="2" t="s">
         <v>131</v>
       </c>
-    </row>
-    <row r="31" s="1" customFormat="1" ht="15.6" spans="1:7">
-      <c r="A31" s="2" t="s">
-        <v>132</v>
-      </c>
-      <c r="B31" s="2" t="s">
-        <v>133</v>
-      </c>
-      <c r="C31" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="D31" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="E31" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="F31" s="2" t="s">
-        <v>100</v>
-      </c>
-      <c r="G31" s="2" t="s">
-        <v>134</v>
-      </c>
-    </row>
-    <row r="32" s="1" customFormat="1" ht="15.6" spans="1:7">
-      <c r="A32" s="2" t="s">
-        <v>135</v>
-      </c>
-      <c r="B32" s="2" t="s">
-        <v>136</v>
-      </c>
-      <c r="C32" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D32" s="2" t="s">
-        <v>58</v>
-      </c>
-      <c r="E32" s="2" t="s">
-        <v>104</v>
-      </c>
-      <c r="F32" s="2" t="s">
-        <v>137</v>
-      </c>
-      <c r="G32" s="2" t="s">
-        <v>138</v>
-      </c>
-    </row>
-    <row r="33" s="1" customFormat="1" ht="15.6" spans="1:7">
-      <c r="A33" s="2" t="s">
-        <v>139</v>
-      </c>
-      <c r="B33" s="2" t="s">
-        <v>140</v>
-      </c>
-      <c r="C33" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D33" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="E33" s="2" t="s">
-        <v>141</v>
-      </c>
-      <c r="F33" s="2" t="s">
-        <v>137</v>
-      </c>
-      <c r="G33" s="2" t="s">
-        <v>142</v>
-      </c>
-    </row>
-    <row r="34" s="1" customFormat="1" ht="15.6" spans="1:7">
-      <c r="A34" s="2" t="s">
-        <v>143</v>
-      </c>
-      <c r="B34" s="2" t="s">
-        <v>144</v>
-      </c>
-      <c r="C34" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D34" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="E34" s="2" t="s">
-        <v>145</v>
-      </c>
-      <c r="F34" s="2" t="s">
-        <v>137</v>
-      </c>
-      <c r="G34" s="2" t="s">
-        <v>146</v>
-      </c>
-    </row>
-    <row r="35" s="1" customFormat="1" ht="15.6" spans="1:7">
-      <c r="A35" s="2" t="s">
-        <v>147</v>
-      </c>
-      <c r="B35" s="2" t="s">
-        <v>148</v>
-      </c>
-      <c r="C35" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D35" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="E35" s="2" t="s">
-        <v>112</v>
-      </c>
-      <c r="F35" s="2" t="s">
-        <v>137</v>
-      </c>
-      <c r="G35" s="2" t="s">
-        <v>149</v>
-      </c>
-    </row>
-    <row r="36" s="1" customFormat="1" ht="15.6" spans="1:7">
-      <c r="A36" s="2" t="s">
-        <v>150</v>
-      </c>
-      <c r="B36" s="2" t="s">
-        <v>151</v>
-      </c>
-      <c r="C36" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D36" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="E36" s="2" t="s">
-        <v>152</v>
-      </c>
-      <c r="F36" s="2" t="s">
-        <v>137</v>
-      </c>
-      <c r="G36" s="2" t="s">
-        <v>153</v>
-      </c>
-    </row>
-    <row r="37" s="1" customFormat="1" ht="15.6" spans="1:7">
-      <c r="A37" s="2" t="s">
+      <c r="F51" s="2" t="s">
         <v>154</v>
-      </c>
-      <c r="B37" s="2" t="s">
-        <v>155</v>
-      </c>
-      <c r="C37" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="D37" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="E37" s="2" t="s">
-        <v>67</v>
-      </c>
-      <c r="F37" s="2" t="s">
-        <v>137</v>
-      </c>
-      <c r="G37" s="2" t="s">
-        <v>156</v>
-      </c>
-    </row>
-    <row r="38" s="1" customFormat="1" ht="15.6" spans="1:7">
-      <c r="A38" s="2" t="s">
-        <v>157</v>
-      </c>
-      <c r="B38" s="2" t="s">
-        <v>158</v>
-      </c>
-      <c r="C38" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D38" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="E38" s="2" t="s">
-        <v>159</v>
-      </c>
-      <c r="F38" s="2" t="s">
-        <v>137</v>
-      </c>
-      <c r="G38" s="2" t="s">
-        <v>160</v>
-      </c>
-    </row>
-    <row r="39" s="1" customFormat="1" ht="15.6" spans="1:7">
-      <c r="A39" s="2" t="s">
-        <v>161</v>
-      </c>
-      <c r="B39" s="2" t="s">
-        <v>162</v>
-      </c>
-      <c r="C39" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="D39" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="E39" s="2" t="s">
-        <v>79</v>
-      </c>
-      <c r="F39" s="2" t="s">
-        <v>137</v>
-      </c>
-      <c r="G39" s="2" t="s">
-        <v>163</v>
-      </c>
-    </row>
-    <row r="40" s="1" customFormat="1" ht="15.6" spans="1:7">
-      <c r="A40" s="2" t="s">
-        <v>164</v>
-      </c>
-      <c r="B40" s="2" t="s">
-        <v>165</v>
-      </c>
-      <c r="C40" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="D40" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="E40" s="2" t="s">
-        <v>79</v>
-      </c>
-      <c r="F40" s="2" t="s">
-        <v>137</v>
-      </c>
-      <c r="G40" s="2" t="s">
-        <v>166</v>
-      </c>
-    </row>
-    <row r="41" s="1" customFormat="1" ht="15.6" spans="1:7">
-      <c r="A41" s="2" t="s">
-        <v>167</v>
-      </c>
-      <c r="B41" s="2" t="s">
-        <v>168</v>
-      </c>
-      <c r="C41" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D41" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="E41" s="2" t="s">
-        <v>169</v>
-      </c>
-      <c r="F41" s="2" t="s">
-        <v>137</v>
-      </c>
-      <c r="G41" s="2" t="s">
-        <v>170</v>
-      </c>
-    </row>
-    <row r="42" s="1" customFormat="1" ht="15.6" spans="1:7">
-      <c r="A42" s="2" t="s">
-        <v>171</v>
-      </c>
-      <c r="B42" s="2" t="s">
-        <v>172</v>
-      </c>
-      <c r="C42" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="D42" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="E42" s="2" t="s">
-        <v>67</v>
-      </c>
-      <c r="F42" s="2" t="s">
-        <v>173</v>
-      </c>
-      <c r="G42" s="2" t="s">
-        <v>174</v>
-      </c>
-    </row>
-    <row r="43" s="1" customFormat="1" ht="15.6" spans="1:7">
-      <c r="A43" s="2" t="s">
-        <v>175</v>
-      </c>
-      <c r="B43" s="2" t="s">
-        <v>176</v>
-      </c>
-      <c r="C43" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D43" s="2" t="s">
-        <v>58</v>
-      </c>
-      <c r="E43" s="2" t="s">
-        <v>108</v>
-      </c>
-      <c r="F43" s="2" t="s">
-        <v>173</v>
-      </c>
-      <c r="G43" s="2" t="s">
-        <v>177</v>
-      </c>
-    </row>
-    <row r="44" s="1" customFormat="1" ht="15.6" spans="1:7">
-      <c r="A44" s="2" t="s">
-        <v>178</v>
-      </c>
-      <c r="B44" s="2" t="s">
-        <v>179</v>
-      </c>
-      <c r="C44" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D44" s="2"/>
-      <c r="E44" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="F44" s="2" t="s">
-        <v>173</v>
-      </c>
-      <c r="G44" s="2" t="s">
-        <v>180</v>
-      </c>
-    </row>
-    <row r="45" s="1" customFormat="1" ht="15.6" spans="1:7">
-      <c r="A45" s="2" t="s">
-        <v>181</v>
-      </c>
-      <c r="B45" s="2" t="s">
-        <v>182</v>
-      </c>
-      <c r="C45" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="D45" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="E45" s="2" t="s">
-        <v>183</v>
-      </c>
-      <c r="F45" s="2" t="s">
-        <v>173</v>
-      </c>
-      <c r="G45" s="2" t="s">
-        <v>184</v>
-      </c>
-    </row>
-    <row r="46" s="1" customFormat="1" ht="15.6" spans="1:7">
-      <c r="A46" s="2" t="s">
-        <v>185</v>
-      </c>
-      <c r="B46" s="2" t="s">
-        <v>186</v>
-      </c>
-      <c r="C46" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D46" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="E46" s="2" t="s">
-        <v>112</v>
-      </c>
-      <c r="F46" s="2" t="s">
-        <v>173</v>
-      </c>
-      <c r="G46" s="2" t="s">
-        <v>187</v>
-      </c>
-    </row>
-    <row r="47" s="1" customFormat="1" ht="15.6" spans="1:7">
-      <c r="A47" s="2" t="s">
-        <v>188</v>
-      </c>
-      <c r="B47" s="2" t="s">
-        <v>189</v>
-      </c>
-      <c r="C47" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="D47" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="E47" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="F47" s="2" t="s">
-        <v>173</v>
-      </c>
-      <c r="G47" s="2" t="s">
-        <v>190</v>
-      </c>
-    </row>
-    <row r="48" s="1" customFormat="1" ht="15.6" spans="1:7">
-      <c r="A48" s="2" t="s">
-        <v>191</v>
-      </c>
-      <c r="B48" s="2" t="s">
-        <v>192</v>
-      </c>
-      <c r="C48" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D48" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="E48" s="2" t="s">
-        <v>193</v>
-      </c>
-      <c r="F48" s="2" t="s">
-        <v>173</v>
-      </c>
-      <c r="G48" s="2" t="s">
-        <v>194</v>
-      </c>
-    </row>
-    <row r="49" s="1" customFormat="1" ht="15.6" spans="1:7">
-      <c r="A49" s="2" t="s">
-        <v>195</v>
-      </c>
-      <c r="B49" s="2" t="s">
-        <v>196</v>
-      </c>
-      <c r="C49" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D49" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="E49" s="2" t="s">
-        <v>197</v>
-      </c>
-      <c r="F49" s="2" t="s">
-        <v>173</v>
-      </c>
-      <c r="G49" s="2" t="s">
-        <v>198</v>
-      </c>
-    </row>
-    <row r="50" s="1" customFormat="1" ht="15.6" spans="1:7">
-      <c r="A50" s="2" t="s">
-        <v>199</v>
-      </c>
-      <c r="B50" s="2" t="s">
-        <v>200</v>
-      </c>
-      <c r="C50" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="D50" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="E50" s="2" t="s">
-        <v>87</v>
-      </c>
-      <c r="F50" s="2" t="s">
-        <v>173</v>
-      </c>
-      <c r="G50" s="2" t="s">
-        <v>201</v>
-      </c>
-    </row>
-    <row r="51" s="1" customFormat="1" ht="15.6" spans="1:7">
-      <c r="A51" s="2" t="s">
-        <v>202</v>
-      </c>
-      <c r="B51" s="2" t="s">
-        <v>203</v>
-      </c>
-      <c r="C51" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="D51" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="E51" s="2" t="s">
-        <v>204</v>
-      </c>
-      <c r="F51" s="2" t="s">
-        <v>173</v>
-      </c>
-      <c r="G51" s="2" t="s">
-        <v>205</v>
       </c>
     </row>
   </sheetData>
